--- a/processed_output/gpo_issue_log_2026-06-02.xlsx
+++ b/processed_output/gpo_issue_log_2026-06-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3778,6 +3778,2368 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>105 Stat. 1761</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>105</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>102 Session 1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Law number reported as 238 between Public Law 102-232 and Public Law 102-234, and a second Public Law 102-238 appears later in the volume</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Should be Public Law 102-233 — the volume table of contents and the bill index both list the Resolution Trust Corporation Act at 105 Stat. 1761 (H.R. 3435) as 102-233, and the surrounding XML order requires 233 in this slot.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>&lt;dc:title&gt;Public Law 102–238: To provide funding for the resolution of failed savings associations and working capital for the Resolution Trust Corporation, to restructure the Oversight Board and the Resolution Trust Corporation, and for other purposes.&lt;/dc:title&gt;
+&lt;dc:type&gt;Public Law&lt;/dc:type&gt;
+&lt;docNumber&gt;238&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 102–238&lt;/citableAs&gt;
+&lt;citableAs&gt;105 Stat. 1761&lt;/citableAs&gt;
+&lt;approvedDate&gt;1991-12-12&lt;/approvedDate&gt;
+...
+&lt;page identifier="/us/stat/105/1761"&gt;105 STAT. 1761&lt;/page&gt;
+&lt;dc:type&gt;Public Law&lt;/dc:type&gt; &lt;docNumber&gt;102–238&lt;/docNumber&gt;</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;meta&gt;
+  &lt;docNumber&gt;
+   &lt;citableAs&gt;</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>94383-94402</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>105 Stat. 1908</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>105</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>102 Session 1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Law number 238 reported a second time on the Technical Amendments to Various Indian Laws Act</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Reviewed: duplicate 238 — no correction needed on this law. This is the genuine Public Law 102-238 (105 Stat. 1908, S. 1193, Dec. 17, 1991) per the volume table of contents; the duplication is caused by the earlier law at 105 Stat. 1761 being misnumbered 238 instead of 233.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>&lt;dc:title&gt;Public Law 102–238: To make technical amendments to various Indian laws.&lt;/dc:title&gt;
+&lt;dc:type&gt;Public Law&lt;/dc:type&gt;
+&lt;docNumber&gt;238&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 102–238&lt;/citableAs&gt;
+&lt;citableAs&gt;105 Stat. 1908&lt;/citableAs&gt;
+&lt;approvedDate&gt;1991-12-17&lt;/approvedDate&gt;
+...
+&lt;page identifier="/us/stat/105/1908"&gt;105 STAT. 1908&lt;/page&gt;
+&lt;dc:type&gt;Public Law&lt;/dc:type&gt; &lt;docNumber&gt;102–238&lt;/docNumber&gt;</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;meta&gt;
+  &lt;docNumber&gt;
+   &lt;citableAs&gt;</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>105907-106094</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>105 Stat. 1793</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>105</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>102 Session 1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Sequence gap before 234 because the preceding law in XML order is reported as 238 instead of 233</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Reviewed: gap — no correction needed on this law. Public Law 102-234 (Medicaid Voluntary Contribution Act, 105 Stat. 1793, H.R. 3595) is correctly numbered; the apparent gap disappears once the preceding law at 105 Stat. 1761 is corrected from 238 to 102-233.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>&lt;dc:title&gt;Public Law 102–234: To delay until September 30, 1992, the issuance of any regulations by the Secretary of Health and Human Services changing the treatment of voluntary contributions and provider-specific taxes by States ...&lt;/dc:title&gt;
+&lt;dc:type&gt;Public Law&lt;/dc:type&gt;
+&lt;docNumber&gt;234&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 102–234&lt;/citableAs&gt;
+&lt;citableAs&gt;105 Stat. 1793&lt;/citableAs&gt;
+&lt;approvedDate&gt;1991-12-12&lt;/approvedDate&gt;</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;meta&gt;
+  &lt;docNumber&gt;
+   &lt;citableAs&gt;</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>96599-97438</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>105 Stat. 1912</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>105</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>102 Session 1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Sequence gap before 239 because the law occupying the 238 slot earlier in XML order is the genuine 102-238</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Reviewed: gap — no correction needed on this law. Public Law 102-239 (105 Stat. 1912, S. 1891) is correctly numbered; the apparent gap disappears once the misnumbered 105 Stat. 1761 law is corrected to 102-233, leaving a single genuine 102-238 immediately before it.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>&lt;dc:title&gt;Public Law 102–239: To permit the Secretary of Health and Human Services to waive certain recovery requirements with respect to the construction or remodeling of facilities, and for other purposes.&lt;/dc:title&gt;
+&lt;dc:type&gt;Public Law&lt;/dc:type&gt;
+&lt;docNumber&gt;239&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 102–239&lt;/citableAs&gt;
+&lt;citableAs&gt;105 Stat. 1912&lt;/citableAs&gt;
+&lt;approvedDate&gt;1991-12-17&lt;/approvedDate&gt;</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;meta&gt;
+  &lt;docNumber&gt;
+   &lt;citableAs&gt;</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>106101-106189</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>107 Stat. 273</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>107</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Law number reported as 103-58 between Public Law 103-52 and Public Law 103-54, where 103-53 was expected, and a second genuine Public Law 103-58 also exists later in the volume</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Should be Public Law 103-53 — the volume's own table of contents lists this title and page 273 as 103-53, and the surrounding XML order requires 53 in this slot.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>&lt;dc:title&gt;Public Law 103–58: Designating July 17 through July 23, 1993, as “National Veterans Golden Age Games Week”.&lt;/dc:title&gt;
+&lt;dc:type&gt;Public Law&lt;/dc:type&gt;
+&lt;docNumber&gt;58&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 103–58&lt;/citableAs&gt;
+&lt;citableAs&gt;107 Stat. 273&lt;/citableAs&gt;
+&lt;approvedDate&gt;1993-07-22&lt;/approvedDate&gt;</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>&lt;statutesAtLarge&gt;
+ &lt;main&gt;
+  &lt;collection&gt;
+   &lt;component&gt;
+    &lt;publicLaws&gt;
+     &lt;component&gt;
+      &lt;pLaw&gt;</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>16658-16712</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>107 Stat. 280</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>107</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Reviewed: duplicate — no correction needed; this is the genuine Public Law 103-58</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>No change — this pLaw (Hot Springs National Park, 107 Stat. 280) is the real Public Law 103-58; the apparent duplicate disappears once the mislabeled 107 Stat. 273 pLaw is renumbered to 103-53.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>&lt;dc:title&gt;Public Law 103–58: To modify the boundary of Hot Springs National Park.&lt;/dc:title&gt;
+&lt;dc:type&gt;Public Law&lt;/dc:type&gt;
+&lt;docNumber&gt;58&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 103–58&lt;/citableAs&gt;
+&lt;citableAs&gt;107 Stat. 280&lt;/citableAs&gt;
+&lt;approvedDate&gt;1993-08-02&lt;/approvedDate&gt;</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>&lt;statutesAtLarge&gt;
+ &lt;main&gt;
+  &lt;collection&gt;
+   &lt;component&gt;
+    &lt;publicLaws&gt;
+     &lt;component&gt;
+      &lt;pLaw&gt;</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>17098-17149</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>107 Stat. 274</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>107</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Reviewed: gap — no correction needed; the apparent gap before Public Law 103-54 is an artifact</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>No change — Public Law 103-54 is correctly numbered; the gap is caused by the mislabeled 107 Stat. 273 pLaw (shown as 103-58 instead of 103-53) and resolves once that pLaw is renumbered.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>&lt;dc:title&gt;Public Law 103–54: To authorize the transfer of naval vessels to certain foreign countries.&lt;/dc:title&gt;
+&lt;dc:type&gt;Public Law&lt;/dc:type&gt;
+&lt;docNumber&gt;54&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 103–54&lt;/citableAs&gt;
+&lt;citableAs&gt;107 Stat. 274&lt;/citableAs&gt;
+&lt;approvedDate&gt;1993-07-28&lt;/approvedDate&gt;</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>&lt;statutesAtLarge&gt;
+ &lt;main&gt;
+  &lt;collection&gt;
+   &lt;component&gt;
+    &lt;publicLaws&gt;
+     &lt;component&gt;
+      &lt;pLaw&gt;</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>16715-16823</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>107 Stat. 281</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>107</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Reviewed: gap — no correction needed; the apparent gap before Public Law 103-59 is an artifact</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>No change — Public Law 103-59 is correctly numbered; the gap is caused by the mislabeled 107 Stat. 273 pLaw (shown as 103-58 instead of 103-53) and resolves once that pLaw is renumbered.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>&lt;dc:title&gt;Public Law 103–59: To extend the operation of the migrant student record transfer system.&lt;/dc:title&gt;
+&lt;dc:type&gt;Public Law&lt;/dc:type&gt;
+&lt;docNumber&gt;59&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 103–59&lt;/citableAs&gt;
+&lt;citableAs&gt;107 Stat. 281&lt;/citableAs&gt;
+&lt;approvedDate&gt;1993-08-02&lt;/approvedDate&gt;</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>&lt;statutesAtLarge&gt;
+ &lt;main&gt;
+  &lt;collection&gt;
+   &lt;component&gt;
+    &lt;publicLaws&gt;
+     &lt;component&gt;
+      &lt;pLaw&gt;</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>17155-17210</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>107</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 108 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>The first SEC. 108 ("Defense Inspector General") sits between SEC. 104 and SEC. 106 and should be SEC. 105; the genuine SEC. 108 is the later "National Shipbuilding Initiative" section.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>&lt;num value="104"&gt;SEC. 104. &lt;/num&gt;
+&lt;heading&gt;DEFENSE-WIDE ACTIVITIES.&lt;/heading&gt;
+...
+&lt;section&gt;
+&lt;num value="108"&gt;SEC. 108. &lt;/num&gt;
+&lt;heading&gt;DEFENSE INSPECTOR GENERAL.&lt;/heading&gt;
+&lt;/section&gt;
+&lt;section&gt;
+&lt;num value="106"&gt;SEC. 106. &lt;/num&gt;</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>92513-92517</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>107</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 128 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>The first SEC. 128 ("Long-Term Lease or Charter Authority for Certain Double-Hull Tankers") sits between SEC. 125 and SEC. 127 and should be SEC. 126; the genuine SEC. 128 is the later "F-14 Aircraft Upgrade Program" section.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>&lt;section&gt;
+&lt;num value="128"&gt;SEC. 128. &lt;/num&gt;
+&lt;heading&gt;LONG-TERM LEASE OR CHARTER AUTHORITY FOR CERTAIN DOUBLE-HULL TANKERS AND OCEANOGRAPHIC VESSELS.&lt;/heading&gt;
+...
+&lt;num value="117"&gt;SEC. 127. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="128"&gt;SEC. 128. &lt;/num&gt;
+&lt;heading&gt;F-14 AIRCRAFT UPGRADE PROGRAM.&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>92750-92751</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>107</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 138 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>The first SEC. 138 ("Intertheater Airlift Program") sits between SEC. 135 and SEC. 137 and should be SEC. 136; the genuine SEC. 138 is the later "Tactical Signals Intelligence Aircraft" section.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>&lt;section&gt;
+&lt;num value="138"&gt;SEC. 138. &lt;/num&gt;
+&lt;heading&gt;INTERTHEATER AIRLIFT PROGRAM.&lt;/heading&gt;
+...
+&lt;num value="137"&gt;SEC. 137. &lt;/num&gt;
+...
+&lt;num value="138"&gt;SEC. 138. &lt;/num&gt;
+&lt;heading&gt;TACTICAL SIGNALS INTELLIGENCE AIRCRAFT.&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>93042-93043</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>107</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 158 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>The first SEC. 158 ("Administration of Chemical Demilitarization Program") sits between SEC. 154 and SEC. 156 and should be SEC. 155; the genuine SEC. 158 is the later "Sales Authority of Certain Working-Capital Funded" section.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>&lt;num value="154"&gt;SEC. 154. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="158"&gt;SEC. 158. &lt;/num&gt;
+&lt;heading&gt;ADMINISTRATION OF CHEMICAL DEMILITARIZATION PROGRAM.&lt;/heading&gt;
+...
+&lt;num value="156"&gt;SEC. 156. &lt;/num&gt;
+&lt;num value="157"&gt;SEC. 157. &lt;/num&gt;
+&lt;num value="158"&gt;SEC. 158. &lt;/num&gt;</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>93430-93431</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>107</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 236 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>The first SEC. 236 ("Theater Missile Defense Master Plan") sits immediately after SEC. 234 and should be SEC. 235; the genuine SEC. 236 is the later "Limited Defense System Development Plan" section.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>&lt;num value="234"&gt;SEC. 234. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="236"&gt;SEC. 236. &lt;/num&gt;
+&lt;heading&gt;THEATER MISSILE DEFENSE MASTER PLAN.&lt;/heading&gt;
+...
+&lt;num value="236"&gt;SEC. 236. &lt;/num&gt;
+&lt;heading&gt;LIMITED DEFENSE SYSTEM DEVELOPMENT PLAN.&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>94300-94301</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>107</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 346 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>The first SEC. 346 ("Sense of Congress on the Role of Depot-Level Activities") sits between SEC. 344 and the genuine SEC. 346 and should be SEC. 345; the genuine SEC. 346 is the later "Contracts to Perform Workloads Previously Performed by Depot-Level Activities" section.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>&lt;num value="344"&gt;SEC. 344. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="346"&gt;SEC. 346. &lt;/num&gt;
+&lt;heading&gt;SENSE OF CONGRESS ON THE ROLE OF DEPOT-LEVEL ACTIVITIES OF THE DEPARTMENT OF DEFENSE.&lt;/heading&gt;
+...
+&lt;num value="346"&gt;SEC. 346. &lt;/num&gt;
+&lt;heading&gt;CONTRACTS TO PERFORM WORKLOADS PREVIOUSLY PERFORMED BY DEPOT-LEVEL ACTIVITIES OF THE DEPARTMENT OF DEFENSE.&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>95714-95715</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>107</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 366 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>The first SEC. 366 ("Extension and Modification of Pilot Program to Use National Guard Personnel") sits between SEC. 364 and the genuine SEC. 366 and should be SEC. 365; the genuine SEC. 366 is the later "Amendments to the Armed Forces Retirement Home Act of 1991" section.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>&lt;num value="364"&gt;SEC. 364. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="366"&gt;SEC. 366. &lt;/num&gt;
+&lt;heading&gt;EXTENSION AND MODIFICATION OF PILOT PROGRAM TO USE NATIONAL GUARD PERSONNEL IN MEDICALLY UNDERSERVED COMMUNITIES.&lt;/heading&gt;
+...
+&lt;num value="366"&gt;SEC. 366. &lt;/num&gt;
+&lt;heading&gt;AMENDMENTS TO THE ARMED FORCES RETIREMENT HOME ACT OF 1991.&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>95959-95960</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>107</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 718 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>The first SEC. 718 ("Specialized Treatment Facility Program Authority") sits between SEC. 715 and SEC. 717 and should be SEC. 716; the genuine SEC. 718 is the later "Managed-Care Delivery and Reimbursement Model" section.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>&lt;num value="715"&gt;SEC. 715. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="718"&gt;SEC. 718. &lt;/num&gt;
+&lt;heading&gt;SPECIALIZED TREATMENT FACILITY PROGRAM AUTHORITY AND ISSUANCE OF NONAVAILABILITY OF HEALTH CARE STATEMENTS.&lt;/heading&gt;
+...
+&lt;num value="717"&gt;SEC. 717. &lt;/num&gt;
+&lt;num value="718"&gt;SEC. 718. &lt;/num&gt;</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>98833-98834</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>107</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 838 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>The first SEC. 838 ("Program Work Force Policies") sits between SEC. 835 and SEC. 837 and should be SEC. 836; the genuine SEC. 838 is the later "Contract Administration: Performance Based Contracting" section.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>&lt;num value="835"&gt;SEC. 835. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="838"&gt;SEC. 838. &lt;/num&gt;
+&lt;heading&gt;PROGRAM WORK FORCE POLICIES.&lt;/heading&gt;
+...
+&lt;num value="837"&gt;SEC. 837. &lt;/num&gt;
+&lt;num value="838"&gt;SEC. 838. &lt;/num&gt;</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>100045-100046</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>107</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 1113 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>The first SEC. 1113 ("Obligation of Certain Appropriations") sits immediately after SEC. 1111 and should be SEC. 1112; the genuine SEC. 1113 is the later "Supplemental Authorization of Appropriations for Fiscal Year 1993" section.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>&lt;num value="1111"&gt;SEC. 1111. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="1113"&gt;SEC. 1113. &lt;/num&gt;
+&lt;heading&gt;OBLIGATION OF CERTAIN APPROPRIATIONS.&lt;/heading&gt;
+...
+&lt;num value="1113"&gt;SEC. 1113. &lt;/num&gt;
+&lt;heading&gt;SUPPLEMENTAL AUTHORIZATION OF APPROPRIATIONS FOR FISCAL YEAR 1993.&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>101537-101538</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>107</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 1176 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>The first SEC. 1176 ("Effective Date for Changes in Servicemen's Group Life Insurance Program") sits immediately after SEC. 1174 and should be SEC. 1175; the genuine SEC. 1176 is the later "Eligibility of Former Prisoners of War for Burial" section.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>&lt;num value="1174"&gt;SEC. 1174. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="1176"&gt;SEC. 1176. &lt;/num&gt;
+&lt;heading&gt;EFFECTIVE DATE FOR CHANGES IN SERVICEMEN’S GROUP LIFE INSURANCE PROGRAM.&lt;/heading&gt;
+...
+&lt;num value="1176"&gt;SEC. 1176. &lt;/num&gt;
+&lt;heading&gt;ELIGIBILITY OF FORMER PRISONERS OF WAR FOR BURIAL...&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>102292-102293</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>107</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 1313 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>The first SEC. 1313 ("Defense Technology and Industrial Base, Reinvestment, and Conversion Planning") sits immediately after SEC. 1311 and should be SEC. 1312; the genuine SEC. 1313 is the later "Congressional Defense Policy Concerning Defense Technology..." section.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>&lt;num value="1311"&gt;SEC. 1311. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="1313"&gt;SEC. 1313. &lt;/num&gt;
+&lt;heading&gt;DEFENSE TECHNOLOGY AND INDUSTRIAL BASE, REINVESTMENT, AND CONVERSION PLANNING.&lt;/heading&gt;
+...
+&lt;num value="1313"&gt;SEC. 1313. &lt;/num&gt;
+&lt;heading&gt;CONGRESSIONAL DEFENSE POLICY CONCERNING DEFENSE TECHNOLOGY AND INDUSTRIAL BASE, REINVESTMENT, AND CONVERSION.&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>103432-103433</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>107</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 1423 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Source XML contains two SEC. 1423 sections ("Report on Effect of Increased Use of Dual-Use Technologies" and "Extension of Landmine Export Moratorium") with no other section number nearby to anchor a confident renumbering; one of the two should carry the next available number (likely SEC. 1424 for the landmine section) but the correct value cannot be determined from XML order alone.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>&lt;num value="1422"&gt;SEC. 1422. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="1423"&gt;SEC. 1423. &lt;/num&gt;
+&lt;heading&gt;REPORT ON EFFECT OF INCREASED USE OF DUAL-USE TECHNOLOGIES ON ABILITY TO CONTROL EXPORTS.&lt;/heading&gt;
+...
+&lt;num value="1423"&gt;SEC. 1423. &lt;/num&gt;
+&lt;heading&gt;EXTENSION OF LANDMINE EXPORT MORATORIUM.&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>105185-105211</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>107</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 1606 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>The first SEC. 1606 ("Joint Committee for Review of Proliferation Programs of the United States") sits immediately after SEC. 1604 and should be SEC. 1605; the genuine SEC. 1606 is the later "Report on Nonproliferation and Counterproliferation" section.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>&lt;num value="1604"&gt;SEC. 1604. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="1606"&gt;SEC. 1606. &lt;/num&gt;
+&lt;heading&gt;JOINT COMMITTEE FOR REVIEW OF PROLIFERATION PROGRAMS OF THE UNITED STATES.&lt;/heading&gt;
+...
+&lt;num value="1606"&gt;SEC. 1606. &lt;/num&gt;
+&lt;heading&gt;REPORT ON NONPROLIFERATION AND COUNTERPROLIFERATION...&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>105998-105999</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>107</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 2918 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>The first SEC. 2918 ("Sense of Congress on Seminars on Reuse or Redevelopment of Property") sits between SEC. 2915 and SEC. 2917 and should be SEC. 2916; the genuine SEC. 2918 is the later "Definitions" section.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>&lt;num value="2915"&gt;SEC. 2915. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="2918"&gt;SEC. 2918. &lt;/num&gt;
+&lt;heading&gt;SENSE OF CONGRESS ON SEMINARS ON REUSE OR REDEVELOPMENT OF PROPERTY AT INSTALLATIONS TO BE CLOSED.&lt;/heading&gt;
+...
+&lt;num value="2917"&gt;SEC. 2917. &lt;/num&gt;
+&lt;num value="2918"&gt;SEC. 2918. &lt;/num&gt;
+&lt;heading&gt;DEFINITIONS.&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>110853-110854</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>107 Stat. 1547</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>107</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>103 Session 1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Two distinct sections both numbered SEC. 3123 collapse to the same unique key</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>The second SEC. 3123 ("Authority for Construction Design") sits between SEC. 3124 and SEC. 3126 and should be SEC. 3125; the first SEC. 3123 ("Limits on Construction Projects") is correctly numbered.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>&lt;num value="3123"&gt;SEC. 3123. &lt;/num&gt;
+&lt;heading&gt;LIMITS ON CONSTRUCTION PROJECTS.&lt;/heading&gt;
+...
+&lt;num value="3124"&gt;SEC. 3124. &lt;/num&gt;
+...
+&lt;section&gt;
+&lt;num value="3123"&gt;SEC. 3123. &lt;/num&gt;
+&lt;heading&gt;AUTHORITY FOR CONSTRUCTION DESIGN.&lt;/heading&gt;
+...
+&lt;num value="3126"&gt;SEC. 3126. &lt;/num&gt;</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;division&gt;
+   &lt;title&gt;
+    &lt;subtitle&gt;
+     &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>111616-111617</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>108</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Law number reported as 333 a second time, duplicating an earlier Public Law 103-333</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>This is the genuine Public Law 103-333 (Labor, Health and Human Services, and Education appropriations); the duplicate is the earlier law at 108 Stat. 2298, which should be Public Law 103-327.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>&lt;docNumber&gt;333&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 103–333&lt;/citableAs&gt;
+&lt;citableAs&gt;108 Stat. 2539&lt;/citableAs&gt;</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>&lt;statutesAtLarge&gt;
+ &lt;main&gt;
+  &lt;collection&gt;
+   &lt;component&gt;
+    &lt;main&gt;
+     &lt;publicLaws&gt;
+      &lt;component&gt;
+       &lt;pLaw&gt;</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>108 Stat. 2576</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>108</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Law number reported as 331 a second time, duplicating an earlier Public Law 103-331</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Should be Public Law 103-334 — the docNumber, preface number, and sequence position all give 334; the citable-as 103-331 is an OCR error.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>&lt;docNumber&gt;334&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 103–331&lt;/citableAs&gt;
+&lt;citableAs&gt;108 Stat. 2576&lt;/citableAs&gt;
+&lt;docNumber&gt;103–334&lt;/docNumber&gt;</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>&lt;statutesAtLarge&gt;
+ &lt;main&gt;
+  &lt;collection&gt;
+   &lt;component&gt;
+    &lt;main&gt;
+     &lt;publicLaws&gt;
+      &lt;component&gt;
+       &lt;pLaw&gt;</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>153241-153850</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>108 Stat. 1557</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>108</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Law number reported as 800 between Public Law 103-299 and Public Law 103-301</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Should be Public Law 103-300 — the Thomas F. Eagleton United States Courthouse designation Act at 108 Stat. 1557 falls in the slot between 103-299 and 103-301.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>&lt;docNumber&gt;800&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 103–800&lt;/citableAs&gt;
+&lt;citableAs&gt;108 Stat. 1557&lt;/citableAs&gt;
+&lt;docNumber&gt;103–800&lt;/docNumber&gt;</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>&lt;statutesAtLarge&gt;
+ &lt;main&gt;
+  &lt;collection&gt;
+   &lt;component&gt;
+    &lt;main&gt;
+     &lt;publicLaws&gt;
+      &lt;component&gt;
+       &lt;pLaw&gt;</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>92351-92401</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>108 Stat. 1558</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>108</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Sequence gap before 301 because the preceding law is misnumbered 800</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Reviewed: gap — no correction needed for this law; the gap is a side effect of the preceding Public Law 103-800 (which should be 103-300). Public Law 103-301 is correct.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>&lt;docNumber&gt;301&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 103–301&lt;/citableAs&gt;
+&lt;citableAs&gt;108 Stat. 1558&lt;/citableAs&gt;</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>&lt;statutesAtLarge&gt;
+ &lt;main&gt;
+  &lt;collection&gt;
+   &lt;component&gt;
+    &lt;main&gt;
+     &lt;publicLaws&gt;
+      &lt;component&gt;
+       &lt;pLaw&gt;</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>92408-92480</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>108 Stat. 2298</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>108</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Law number reported as 333 between Public Law 103-326 and Public Law 103-328</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Should be Public Law 103-327 — the docNumber, preface number, and sequence position all give 327; the citable-as 103-333 is an OCR error (the genuine 103-333 is the Labor/HHS appropriations at 108 Stat. 2539).</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>&lt;docNumber&gt;327&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 103–333&lt;/citableAs&gt;
+&lt;citableAs&gt;108 Stat. 2298&lt;/citableAs&gt;
+&lt;docNumber&gt;103–327&lt;/docNumber&gt;</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>&lt;statutesAtLarge&gt;
+ &lt;main&gt;
+  &lt;collection&gt;
+   &lt;component&gt;
+    &lt;main&gt;
+     &lt;publicLaws&gt;
+      &lt;component&gt;
+       &lt;pLaw&gt;</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>145700-146486</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>108 Stat. 2338</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>108</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Sequence gap before 328 because the preceding law is misnumbered 333</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Reviewed: gap — no correction needed for this law; the gap is a side effect of the preceding law at 108 Stat. 2298 (which should be 103-327, not 103-333). Public Law 103-328 is correct.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>&lt;docNumber&gt;328&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 103–328&lt;/citableAs&gt;
+&lt;citableAs&gt;108 Stat. 2338&lt;/citableAs&gt;</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>&lt;statutesAtLarge&gt;
+ &lt;main&gt;
+  &lt;collection&gt;
+   &lt;component&gt;
+    &lt;main&gt;
+     &lt;publicLaws&gt;
+      &lt;component&gt;
+       &lt;pLaw&gt;</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>146493-148236</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>108 Stat. 2599</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>108</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Sequence gap before 335 because the preceding law is misnumbered 331</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Reviewed: gap — no correction needed for this law; the gap is a side effect of the preceding law at 108 Stat. 2576 (which should be 103-334, not 103-331). Public Law 103-335 is correct.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>&lt;docNumber&gt;335&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 103–335&lt;/citableAs&gt;
+&lt;citableAs&gt;108 Stat. 2599&lt;/citableAs&gt;</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>&lt;statutesAtLarge&gt;
+ &lt;main&gt;
+  &lt;collection&gt;
+   &lt;component&gt;
+    &lt;main&gt;
+     &lt;publicLaws&gt;
+      &lt;component&gt;
+       &lt;pLaw&gt;</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>153857-155428</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>108 Stat. 1796</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>108</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Two different sections both numbered SEC. 230206 in the same law</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>The two sections share section number 230206 in the source; the second (Maintenance of Effort) should be numbered 230207 so the sections can be distinguished.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>&lt;section class="fontsize10"&gt;
+&lt;num value="230206"&gt;SEC. 230206. &lt;/num&gt;
+&lt;heading&gt;ADMINISTRATIVE COSTS FOR CRIME VICTIM ASSISTANCE.&lt;/heading&gt;
+...
+&lt;/section&gt;
+&lt;section class="fontsize10"&gt;
+&lt;num value="230206"&gt;SEC. 230206. &lt;/num&gt;
+&lt;heading&gt;MAINTENANCE OF EFFORT.&lt;/heading&gt;
+...
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>128570-128596</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>108</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Section 503 collides across two laws sharing the law number 103-333</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Resolved by correcting the VA/HUD appropriations law (108 Stat. 2298) from Public Law 103-333 to Public Law 103-327; once renumbered, its TITLE V Sec. 503 no longer collides with the genuine Public Law 103-333 Sec. 503.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>&lt;section class="firstIndent1 fontsize10"&gt;
+&lt;num value="503"&gt;&lt;inline class="smallCaps"&gt;Sec&lt;/inline&gt;. 503.&lt;/num&gt; &lt;content class="inline"&gt;No part of any appropriation contained in this Act shall remain available for obligation beyond the current fiscal year unless expressly so provided herein.&lt;/content&gt;
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>108</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Section 505 collides across two laws sharing the law number 103-333</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Resolved by correcting the VA/HUD appropriations law (108 Stat. 2298) from Public Law 103-333 to Public Law 103-327; once renumbered, its TITLE V Sec. 505 no longer collides with the genuine Public Law 103-333 Sec. 505.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>&lt;section class="firstIndent1 fontsize10"&gt;
+&lt;num value="505"&gt;&lt;inline class="smallCaps"&gt;Sec&lt;/inline&gt;. 505.&lt;/num&gt; &lt;content class="inline"&gt;The Secretaries of Labor and Education are each authorized to make available not to exceed $15,000 from funds available for salaries and expenses under titles I and III, respectively, for official reception and representation expenses; ...&lt;/content&gt;
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>108</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Section 506 collides across two laws sharing the law number 103-333</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Resolved by correcting the VA/HUD appropriations law (108 Stat. 2298) from Public Law 103-333 to Public Law 103-327; once renumbered, its TITLE V Sec. 506 no longer collides with the genuine Public Law 103-333 Sec. 506.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>&lt;section class="firstIndent1 fontsize10"&gt;
+&lt;num value="506"&gt;&lt;inline class="smallCaps"&gt;Sec&lt;/inline&gt;. 506.&lt;/num&gt; &lt;content class="inline"&gt;Notwithstanding any other provision of this Act, no funds appropriated under this Act shall be used to carry out any program of distributing sterile needles for the hypodermic injection of any illegal drug ...&lt;/content&gt;
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>108</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Section 507 collides across two laws sharing the law number 103-333</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Resolved by correcting the VA/HUD appropriations law (108 Stat. 2298) from Public Law 103-333 to Public Law 103-327; once renumbered, its TITLE V Sec. 507 no longer collides with the genuine Public Law 103-333 Sec. 507.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>&lt;section class="firstIndent1 fontsize10"&gt;
+&lt;num value="507"&gt;SEC. 507.&lt;/num&gt; &lt;subsection class="inline"&gt;&lt;num value="a"&gt;(a)&lt;/num&gt; &lt;heading&gt;&lt;inline class="smallCaps"&gt;Purchase of American-Made Equipment and Products&lt;/inline&gt;.—&lt;/heading&gt;&lt;content class="inline"&gt;It is the sense of the Congress that, to the greatest extent practicable, all equipment and products purchased with funds made available in this Act should be American-made.&lt;/content&gt;
+&lt;/subsection&gt;
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>108</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Section 508 collides across two laws sharing the law number 103-333</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Resolved by correcting the VA/HUD appropriations law (108 Stat. 2298) from Public Law 103-333 to Public Law 103-327; once renumbered, its TITLE V Sec. 508 no longer collides with the genuine Public Law 103-333 Sec. 508.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>&lt;section class="firstIndent1 fontsize10"&gt;
+&lt;num value="508"&gt;&lt;inline class="smallCaps"&gt;Sec&lt;/inline&gt;. 508.&lt;/num&gt; &lt;content class="inline"&gt;When issuing statements, press releases, requests for proposals, bid solicitations and other documents describing projects or programs funded in whole or in part with Federal money, all grantees receiving Federal funds ...&lt;/content&gt;
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>108</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Section 509 collides across two laws sharing the law number 103-333</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Resolved by correcting the VA/HUD appropriations law (108 Stat. 2298) from Public Law 103-333 to Public Law 103-327; once renumbered, its TITLE V Sec. 509 no longer collides with the genuine Public Law 103-333 Sec. 509.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>&lt;section class="firstIndent1 fontsize10"&gt;
+&lt;num value="509"&gt;&lt;inline class="smallCaps"&gt;Sec&lt;/inline&gt;. 509.&lt;/num&gt; &lt;content class="inline"&gt;None of the funds appropriated under this Act shall&lt;sidenote&gt;&lt;p class="indent0 firstIndent0 fontsize8"&gt;Abortion.&lt;/p&gt;&lt;/sidenote&gt; be expended for any abortion except when it is made known to the Federal entity or official ...&lt;/content&gt;
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>108</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Section 510 collides across two laws sharing the law number 103-333</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Resolved by correcting the VA/HUD appropriations law (108 Stat. 2298) from Public Law 103-333 to Public Law 103-327; once renumbered, its TITLE V Sec. 510 no longer collides with the genuine Public Law 103-333 Sec. 510.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>&lt;section class="firstIndent1 fontsize10"&gt;
+&lt;num value="510"&gt;&lt;inline class="smallCaps"&gt;Sec&lt;/inline&gt;. 510.&lt;/num&gt; &lt;content class="inline"&gt;No funds appropriated herein shall be used to implement any regulation promulgated under section 481(b)(6) of the Higher Education Act of 1965, as amended, prior to July 1, 1995.&lt;/content&gt;
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>108</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Section 511 collides across two laws sharing the law number 103-333</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Resolved by correcting the VA/HUD appropriations law (108 Stat. 2298) from Public Law 103-333 to Public Law 103-327; once renumbered, its TITLE V Sec. 511 no longer collides with the genuine Public Law 103-333 Sec. 511.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>&lt;section class="firstIndent1 fontsize10"&gt;
+&lt;num value="511"&gt;&lt;inline class="smallCaps"&gt;Sec&lt;/inline&gt;. 511.&lt;/num&gt; &lt;content class="inline"&gt;None of the funds appropriated or otherwise made available under this Act may be obligated in violation of existing Federal law or regulation already prohibiting such benefit or assistance. ...&lt;/content&gt;
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>108</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Section 512 collides across two laws sharing the law number 103-333</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Resolved by correcting the VA/HUD appropriations law (108 Stat. 2298) from Public Law 103-333 to Public Law 103-327; once renumbered, its TITLE V Sec. 512 no longer collides with the genuine Public Law 103-333 Sec. 512.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>&lt;section class="firstIndent1 fontsize10"&gt;
+&lt;num value="512"&gt;&lt;inline class="smallCaps"&gt;Sec&lt;/inline&gt;. 512.&lt;/num&gt; &lt;content class="inline"&gt;Notwithstanding any other provision of law, monthly&lt;sidenote&gt;&lt;p class="indent0 firstIndent0 fontsize8"&gt;&lt;ref href="/us/usc/t30/s922"&gt;30 USC 922 note&lt;/ref&gt;.&lt;/p&gt;&lt;/sidenote&gt; benefit rates during fiscal year 1995 and thereafter under part B or part C of the Black Lung Benefits Act ...&lt;/content&gt;
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>108</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Section 513 collides across two laws sharing the law number 103-333</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Resolved by correcting the VA/HUD appropriations law (108 Stat. 2298) from Public Law 103-333 to Public Law 103-327; once renumbered, its TITLE V Sec. 513 no longer collides with the genuine Public Law 103-333 Sec. 513.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>&lt;section class="firstIndent1 fontsize10"&gt;
+&lt;num value="513"&gt;&lt;inline class="smallCaps"&gt;Sec&lt;/inline&gt;. 513.&lt;/num&gt; &lt;content class="inline"&gt;No more than one percent of salaries appropriated for each Agency in this Act may be expended by that Agency on cash performance awards: &lt;proviso&gt;&lt;i&gt;Provided,&lt;/i&gt; ...&lt;/proviso&gt;&lt;/content&gt;
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>108</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Section 514 collides across two laws sharing the law number 103-333</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Resolved by correcting the VA/HUD appropriations law (108 Stat. 2298) from Public Law 103-333 to Public Law 103-327; once renumbered, its TITLE V Sec. 514 no longer collides with the genuine Public Law 103-333 Sec. 514.</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>&lt;section class="firstIndent1 fontsize10"&gt;
+&lt;num value="514"&gt;&lt;inline class="smallCaps"&gt;Sec&lt;/inline&gt;. 514.&lt;/num&gt; &lt;content class="inline"&gt;Chapter 51 of title 18,United States Code, is amended by adding at the end thereof the following new section: ...&lt;/content&gt;
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>108 Stat. 2539</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>108</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Section 515 collides across two laws sharing the law number 103-333</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Resolved by correcting the VA/HUD appropriations law (108 Stat. 2298) from Public Law 103-333 to Public Law 103-327; once renumbered, its TITLE V Sec. 515 no longer collides with the genuine Public Law 103-333 Sec. 515.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>&lt;section class="firstIndent1 fontsize10"&gt;
+&lt;num value="515"&gt;&lt;inline class="smallCaps"&gt;Sec&lt;/inline&gt;. 515.&lt;/num&gt; &lt;chapeau class="inline"&gt;&lt;sidenote&gt;&lt;p class="indent0 firstIndent0 fontsize8"&gt;&lt;ref href="/us/usc/t31/s1301"&gt;31 USC 1301 note&lt;/ref&gt;.&lt;/p&gt;&lt;/sidenote&gt;Notwithstanding any other provision of law—&lt;/chapeau&gt;
+...
+&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>152268-153234</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>108 Stat. 4398</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>108</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Two different sections both numbered SEC. 206 in the same law</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>The two TITLE II Subtitle A sections share section number 206 in the source; the second (Dispositional Hearing) should be numbered 207 so the sections can be distinguished.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>&lt;num value="206"&gt;SEC. 206. &lt;/num&gt;&lt;heading&gt;CHILD WELFARE TRAINEESHIPS.&lt;/heading&gt;
+...
+&lt;num value="206"&gt;SEC. 206. &lt;/num&gt;&lt;heading&gt;DISPOSITIONAL HEARING.&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>281965-282028</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Public Law 103–465</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>108</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>103 Session 2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Two different sections both numbered SEC. 128 in the same law</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>The two TITLE I Subtitle C sections share section number 128 in the source; the second (Advisory Committee Participation) should be numbered 129 so the sections can be distinguished.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>&lt;num value="128"&gt;SEC. 128. &lt;/num&gt;&lt;heading&gt;&lt;sidenote&gt;&lt;p class="indent0 firstIndent0 fontsize8"&gt;&lt;ref href="/us/usc/t19/s3536"&gt;19 USC 3536&lt;/ref&gt;.&lt;/p&gt;&lt;/sidenote&gt;INCREASED TRANSPARENCY.&lt;/heading&gt;
+...
+&lt;num value="128"&gt;SEC. 128. &lt;/num&gt;&lt;heading&gt;ADVISORY COMMITTEE PARTICIPATION.&lt;/heading&gt;</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;main&gt;
+  &lt;title&gt;
+   &lt;subtitle&gt;
+    &lt;section&gt;</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>308844-308912</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>109 Stat. 961</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>109</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>104 Session 1</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Sequence gap in public law numbers: Public Law 104-93 follows Public Law 104-89, so Public Laws 104-90, 104-91, and 104-92 are absent between them</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>No correction needed - legitimate gap. The docNumber, citableAs, Statutes page (109 Stat. 961), and approval date (Jan. 6, 1996) are internally consistent and follow Public Law 104-89 (109 Stat. 960, Jan. 4, 1996); Public Laws 104-90, 104-91, and 104-92 simply are not printed in this volume slot, not a misnumbering.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>&lt;docNumber&gt;93&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 104–93&lt;/citableAs&gt;
+&lt;citableAs&gt;109 Stat. 961&lt;/citableAs&gt;
+&lt;approvedDate&gt;1996-01-06&lt;/approvedDate&gt;</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;meta&gt;
+  &lt;docNumber&gt;
+   &lt;citableAs&gt;</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>51901-52947</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>109 Stat. 979</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>109</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>104 Session 1</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Sequence gap in public law numbers: Public Law 104-95 follows Public Law 104-93, so Public Law 104-94 is absent between them</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>No correction needed - legitimate gap. The docNumber, citableAs, Statutes page (109 Stat. 979), and approval date (Jan. 10, 1996) are internally consistent and follow Public Law 104-93 (109 Stat. 961, Jan. 6, 1996); Public Law 104-94 simply is not printed in this volume slot, not a misnumbering.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>&lt;docNumber&gt;95&lt;/docNumber&gt;
+&lt;citableAs&gt;Public Law 104–95&lt;/citableAs&gt;
+&lt;citableAs&gt;109 Stat. 979&lt;/citableAs&gt;
+&lt;approvedDate&gt;1996-01-10&lt;/approvedDate&gt;</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>&lt;pLaw&gt;
+ &lt;meta&gt;
+  &lt;docNumber&gt;
+   &lt;citableAs&gt;</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>52953-53103</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
